--- a/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>418562</v>
+        <v>277738</v>
       </c>
       <c r="C2">
-        <v>73.8199</v>
+        <v>73.3112</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>44607</v>
+        <v>28892</v>
       </c>
       <c r="C3">
-        <v>7.8671</v>
+        <v>7.6263</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>70961</v>
+        <v>50649</v>
       </c>
       <c r="C4">
-        <v>12.5151</v>
+        <v>13.3692</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>32874</v>
+        <v>21569</v>
       </c>
       <c r="C5">
-        <v>5.7978</v>
+        <v>5.6933</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>277738</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>73.3112</v>
+        <v>73.8608</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>28892</v>
+        <v>42557</v>
       </c>
       <c r="C3">
-        <v>7.6263</v>
+        <v>7.9138</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>50649</v>
+        <v>67002</v>
       </c>
       <c r="C4">
-        <v>13.3692</v>
+        <v>12.4596</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>21569</v>
+        <v>31006</v>
       </c>
       <c r="C5">
-        <v>5.6933</v>
+        <v>5.7658</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_per_specialty_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,53 +374,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>397191</v>
+        <v>1720623</v>
       </c>
       <c r="C2">
-        <v>73.8608</v>
+        <v>45.2172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>42557</v>
+        <v>1028274</v>
       </c>
       <c r="C3">
-        <v>7.9138</v>
+        <v>27.0226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>67002</v>
+        <v>431420</v>
       </c>
       <c r="C4">
-        <v>12.4596</v>
+        <v>11.3375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>537188</v>
+      </c>
+      <c r="C5">
+        <v>14.1171</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="B5">
-        <v>31006</v>
-      </c>
-      <c r="C5">
-        <v>5.7658</v>
+      <c r="B6">
+        <v>87733</v>
+      </c>
+      <c r="C6">
+        <v>2.3056</v>
       </c>
     </row>
   </sheetData>
